--- a/Analysis/Prompt_Ablation/prompt_ablation_significance.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_significance.xlsx
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.772027972027817</v>
+        <v>1.907647907647787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2500701036036889</v>
+        <v>0.3852649676223279</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.291828793774092</v>
+        <v>2.758754863813109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3179330678270239</v>
+        <v>0.2517352266048014</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01348314606721952</v>
+        <v>0.09438202247213084</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9932811003897493</v>
+        <v>0.9539051735812136</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -662,7 +662,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.9932811003897493</v>
+        <v>1</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13.04859335038335</v>
+        <v>21.92741935483857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001467350808429939</v>
+        <v>1.731894312100037e-05</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -713,7 +713,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.03521641940231854</v>
+        <v>0.0004156546349040089</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11.33913043478107</v>
+        <v>10.83928571428633</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003449364673897372</v>
+        <v>0.0044287280540101</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -764,7 +764,7 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0.07588602282574219</v>
+        <v>0.0930032891342121</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.438547486033578</v>
+        <v>0.4336283185840386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8031018445388534</v>
+        <v>0.8050795719610732</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.351297405189388</v>
+        <v>1.76518218623498</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3086187129783954</v>
+        <v>0.413709561709252</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2063157894736689</v>
+        <v>0.02935010482211944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9019845436252056</v>
+        <v>0.9854321013677525</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -968,7 +968,7 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.9854321013677525</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.00264550264539</v>
+        <v>12.57181208053679</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006729040262777443</v>
+        <v>0.001862368823980613</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1019,10 +1019,10 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.1413098455183263</v>
+        <v>0.04283448295155409</v>
       </c>
       <c r="S11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.233628318584213</v>
+        <v>1.841549295774702</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3273209276362922</v>
+        <v>0.3982104486919231</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5952380952378787</v>
+        <v>0.5516074450082356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7425841750805919</v>
+        <v>0.7589618832806699</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0.8807688599048051</v>
+        <v>0.9233225810589356</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>7686.5</v>
+        <v>7635.5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.01303287108371854</v>
+        <v>0.008376623376623376</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0126758711374096</v>
+        <v>-0.004023668639053254</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>0.1715770268549506</v>
+        <v>0.2341762350536877</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3791</v>
+        <v>3808.5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.1362497151970836</v>
+        <v>0.1190145732130465</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0821301775147929</v>
+        <v>0.07229454306377384</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0.008282243600190314</v>
+        <v>0.01286441172364076</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1308,7 +1308,7 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1576.5</v>
+        <v>1692.5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1321,18 +1321,18 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3085526315789474</v>
+        <v>0.2878182200715338</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>small</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P16" t="n">
-        <v>0.08118343195266273</v>
+        <v>0.07784352399737016</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0.1656448720038063</v>
+        <v>0.2572882344728152</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>0.6509169543061128</v>
+        <v>0.7214344992646248</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3010.5</v>
+        <v>926</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.04851453855878635</v>
+        <v>0.05171530977982591</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.02082840236686391</v>
+        <v>0.01233399079552926</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.03451250539565668</v>
+        <v>0.09762112338522023</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>164.5</v>
+        <v>189.5</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.4135472370766489</v>
+        <v>0.3244206773618538</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>33</v>
       </c>
       <c r="P18" t="n">
-        <v>0.03326758711374096</v>
+        <v>0.02274819197896121</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>0.6212250971218203</v>
+        <v>1</v>
       </c>
       <c r="S18" t="b">
         <v>0</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>0.3903891403830421</v>
+        <v>0.2602755536860685</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>154</v>
+        <v>154.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-0.1851851851851852</v>
+        <v>-0.2389162561576355</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01186061801446417</v>
+        <v>-0.01627876397107166</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>0.07254039512328656</v>
+        <v>0.08094797166424243</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1600,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>6039</v>
+        <v>5138</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.1592064044552732</v>
+        <v>0.1608688551363711</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04131492439184747</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>0.001743496912838276</v>
+        <v>0.00204193628054538</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1673,7 +1673,7 @@
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2149</v>
+        <v>2251.5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3327123117528334</v>
+        <v>0.324887556221889</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1136620644312952</v>
+        <v>0.1091387245233399</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>0.04010042899528035</v>
+        <v>0.04492259817199836</v>
       </c>
       <c r="S21" t="b">
         <v>1</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.3306491040301512</v>
+        <v>0.3837245232320642</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1746,7 +1746,7 @@
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>1770.5</v>
+        <v>1795</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.1158551810237203</v>
+        <v>0.1036204744069913</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>89</v>
       </c>
       <c r="P22" t="n">
-        <v>0.05067718606180144</v>
+        <v>0.0482577251808021</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>0.0963371145999003</v>
+        <v>0.1451341377813551</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>7725.5</v>
+        <v>7456.5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-0.1394597605123921</v>
+        <v>-0.1237955346650999</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1079026955950033</v>
+        <v>-0.08907297830374754</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>0.2693573467437352</v>
+        <v>0.2534826383210801</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1892,7 +1892,7 @@
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>3786.5</v>
+        <v>3770.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.1106283029947152</v>
+        <v>0.1143863769817968</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130</v>
       </c>
       <c r="P24" t="n">
-        <v>0.06574621959237344</v>
+        <v>0.06966469428007889</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.1656555999789144</v>
+        <v>0.1717908742652029</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>3492</v>
+        <v>3557.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.140748031496063</v>
+        <v>0.138202519379845</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05593688362919132</v>
+        <v>0.05577909270216962</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>520.5</v>
+        <v>526.5</v>
       </c>
       <c r="G2" t="n">
-        <v>6.282327479267287e-05</v>
+        <v>7.34278993374151e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5562659846547314</v>
+        <v>0.551150895140665</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04817882971729125</v>
+        <v>0.04904667981591058</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>195</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001884698243780186</v>
+        <v>0.0002202836980122453</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2071</v>
+        <v>508.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004625170486324907</v>
+        <v>0.002625479855890568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3090909090909091</v>
+        <v>0.4442622950819672</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02406311637080868</v>
+        <v>0.03702827087442472</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>195</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009250340972649814</v>
+        <v>0.005250959711781137</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -2243,24 +2243,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1906.5</v>
+        <v>361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06090764123510683</v>
+        <v>0.07588327712701348</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2139764996907854</v>
+        <v>-0.3024154589371981</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01964497041420118</v>
+        <v>-0.01094017094017094</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2271,9 +2271,192 @@
         <v>195</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06090764123510683</v>
+        <v>0.07588327712701348</v>
       </c>
       <c r="O4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6036.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0004319605796425415</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.2982853821563499</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>185</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.1604733727810651</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>195</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001295881738927624</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>no_anchors</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7325</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03694021336660368</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1753911966677924</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>188</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1359105851413544</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>195</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07388042673320735</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>no_anchors</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7633</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7210640201653558</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.03091474639751159</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>177</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.007337278106508876</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>195</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7210640201653558</v>
+      </c>
+      <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2355,22 +2538,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1386542815293522</v>
+        <v>0.1339031339031339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5339046297307454</v>
+        <v>0.5429143044252263</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4</v>
+        <v>0.3914529914529915</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3793042403642553</v>
+        <v>0.3784515043749799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7418803418803418</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3333950070709812</v>
+        <v>0.3377711460131516</v>
       </c>
     </row>
     <row r="3">
@@ -2390,22 +2573,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1795072379149357</v>
+        <v>0.1863247863247863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6423119172092501</v>
+        <v>0.6552402873380349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.388034188034188</v>
+        <v>0.3897435897435897</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4272697077701155</v>
+        <v>0.4290532643790659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7316239316239316</v>
+        <v>0.7282051282051282</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3936748414022372</v>
+        <v>0.3971215490449165</v>
       </c>
     </row>
     <row r="4">
@@ -2425,22 +2608,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1872341412776441</v>
+        <v>0.1943019943019943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5024618424304014</v>
+        <v>0.5099672929769843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.452991452991453</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3744960683315097</v>
+        <v>0.3754751446907683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7658119658119659</v>
+        <v>0.7606837606837608</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3090360414008668</v>
+        <v>0.3115633081892658</v>
       </c>
     </row>
     <row r="5">
@@ -2460,22 +2643,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1604735729247735</v>
+        <v>0.166951566951567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7415147611035319</v>
+        <v>0.7542146951706779</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3948717948717949</v>
+        <v>0.3931623931623932</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4697942849707798</v>
+        <v>0.4694065058828521</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7008547008547008</v>
+        <v>0.6957264957264957</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4527810955358428</v>
+        <v>0.4550329146849775</v>
       </c>
     </row>
     <row r="6">
@@ -2495,22 +2678,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1804741544144793</v>
+        <v>0.1897435897435897</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7238083873879905</v>
+        <v>0.7374739253717284</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.4068376068376068</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4683290507159157</v>
+        <v>0.4686738551933322</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7128205128205128</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4459705932276149</v>
+        <v>0.4483942036669344</v>
       </c>
     </row>
     <row r="7">
@@ -2530,22 +2713,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.109306644736094</v>
+        <v>0.1168091168091168</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7531817980100469</v>
+        <v>0.7686209126659908</v>
       </c>
       <c r="F7" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3606837606837607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4676512403653051</v>
+        <v>0.4693877342529448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.6837606837606838</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4516314662316711</v>
+        <v>0.4537530775393062</v>
       </c>
     </row>
     <row r="8">
@@ -2565,22 +2748,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04757544012981867</v>
+        <v>0.04615384615384616</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5260945148559988</v>
+        <v>0.5253745759842307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3572649572649572</v>
+        <v>0.3504273504273504</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3375971895994851</v>
+        <v>0.3380145345899075</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6871794871794872</v>
+        <v>0.6820512820512821</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3292373241503922</v>
+        <v>0.3303861250555453</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2783,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05635269486357057</v>
+        <v>0.06381766381766382</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5062823460444676</v>
+        <v>0.5032459102213337</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3196581196581196</v>
+        <v>0.3179487179487179</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3547031371513891</v>
+        <v>0.3538243163508289</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6735042735042736</v>
+        <v>0.676923076923077</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3315398043635254</v>
+        <v>0.327977055304273</v>
       </c>
     </row>
     <row r="10">
@@ -2635,22 +2818,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06378597559579201</v>
+        <v>0.06324786324786325</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4945120526300915</v>
+        <v>0.4966359649671256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3435897435897436</v>
+        <v>0.3401709401709401</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3348893105119662</v>
+        <v>0.3349770031240409</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6991452991452992</v>
+        <v>0.6957264957264957</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3326011873081748</v>
+        <v>0.3311941225368422</v>
       </c>
     </row>
     <row r="11">
@@ -2670,22 +2853,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01341909416365631</v>
+        <v>-0.01025641025641026</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4133722962402352</v>
+        <v>0.4134633229266262</v>
       </c>
       <c r="F11" t="n">
         <v>0.2957264957264957</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3115915879927992</v>
+        <v>0.3097480303982494</v>
       </c>
       <c r="H11" t="n">
         <v>0.6478632478632479</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3178351449567761</v>
+        <v>0.317835144956776</v>
       </c>
     </row>
     <row r="12">
@@ -2705,22 +2888,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.12517762581901</v>
+        <v>0.1230769230769231</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4942395180504723</v>
+        <v>0.5077193640430837</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2991452991452991</v>
+        <v>0.3094017094017094</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3417734875749093</v>
+        <v>0.34762726397558</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6273504273504273</v>
+        <v>0.6205128205128205</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3470437906148749</v>
+        <v>0.3527518544609275</v>
       </c>
     </row>
     <row r="13">
@@ -2740,22 +2923,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.006382929361177935</v>
+        <v>0.01196581196581196</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4458994284986409</v>
+        <v>0.442200698096608</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3418803418803418</v>
+        <v>0.3401709401709401</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3164738017055699</v>
+        <v>0.313789560302139</v>
       </c>
       <c r="H13" t="n">
-        <v>0.67008547008547</v>
+        <v>0.6683760683760684</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3120154774661034</v>
+        <v>0.3111104817284018</v>
       </c>
     </row>
     <row r="14">
@@ -2775,22 +2958,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2811619855261805</v>
+        <v>0.2757834757834758</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5113807669965317</v>
+        <v>0.5211992600440187</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4991452991452991</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3893989832118382</v>
+        <v>0.3907918898492002</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8222222222222223</v>
+        <v>0.8153846153846154</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2755119501395925</v>
+        <v>0.2792813303878656</v>
       </c>
     </row>
     <row r="15">
@@ -2810,22 +2993,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2343490890339761</v>
+        <v>0.2393162393162394</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6117380189666508</v>
+        <v>0.630630908465899</v>
       </c>
       <c r="F15" t="n">
         <v>0.4444444444444445</v>
       </c>
       <c r="G15" t="n">
-        <v>0.409881756853111</v>
+        <v>0.4098817568531109</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7367521367521367</v>
+        <v>0.7316239316239316</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3756471980455561</v>
+        <v>0.3788471024440885</v>
       </c>
     </row>
     <row r="16">
@@ -2845,22 +3028,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2997610314676699</v>
+        <v>0.3014245014245014</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6735854137251773</v>
+        <v>0.6884526363525846</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4837606837606838</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.477612895134348</v>
+        <v>0.4773299308606253</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7726495726495726</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3977940169102152</v>
+        <v>0.398693787606885</v>
       </c>
     </row>
     <row r="17">
@@ -2880,10 +3063,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2869692994205</v>
+        <v>0.2968660968660968</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6656282468042715</v>
+        <v>0.6766621276251</v>
       </c>
       <c r="F17" t="n">
         <v>0.4598290598290599</v>
@@ -2915,22 +3098,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.2422428621396842</v>
+        <v>0.2512820512820513</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5565926208633349</v>
+        <v>0.5603266798866464</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4752136752136752</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3805102982261166</v>
+        <v>0.3811658390173345</v>
       </c>
       <c r="H18" t="n">
         <v>0.7675213675213675</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3411025163498578</v>
+        <v>0.3394192853800819</v>
       </c>
     </row>
     <row r="19">
@@ -2950,16 +3133,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2001927430678137</v>
+        <v>0.2125356125356125</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5162487478579981</v>
+        <v>0.5201500373856168</v>
       </c>
       <c r="F19" t="n">
-        <v>0.388034188034188</v>
+        <v>0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3523352937071527</v>
+        <v>0.3543220298003396</v>
       </c>
       <c r="H19" t="n">
         <v>0.7487179487179487</v>
@@ -2985,22 +3168,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1317908013669313</v>
+        <v>0.1350427350427351</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4877694385637601</v>
+        <v>0.4945260911876473</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4427350427350427</v>
+        <v>0.4376068376068376</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3637299388034241</v>
+        <v>0.3597106103608234</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7401709401709402</v>
+        <v>0.72991452991453</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3224316515814652</v>
+        <v>0.3263701290814409</v>
       </c>
     </row>
     <row r="21">
@@ -3020,22 +3203,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2024402571251442</v>
+        <v>0.2011396011396011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5447218826129794</v>
+        <v>0.5628376964729025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4017094017094017</v>
+        <v>0.3948717948717949</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3782419025985486</v>
+        <v>0.3763892526413594</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.6803418803418803</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3739309567860317</v>
+        <v>0.3735773279689106</v>
       </c>
     </row>
   </sheetData>
